--- a/excel/output_stats_vfvv/2mm/PerSubgraphStats.xlsx
+++ b/excel/output_stats_vfvv/2mm/PerSubgraphStats.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O32"/>
+  <dimension ref="A1:O33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,7 +529,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K2" t="n">
         <v>68</v>
@@ -576,7 +576,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K3" t="n">
         <v>58</v>
@@ -670,7 +670,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K5" t="n">
         <v>60</v>
@@ -858,7 +858,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>13</v>
@@ -952,7 +952,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K11" t="n">
         <v>20</v>
@@ -1093,7 +1093,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>961200</v>
+        <v>3360190</v>
       </c>
       <c r="K14" t="n">
         <v>15835800</v>
@@ -1187,7 +1187,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1081200</v>
+        <v>4319390</v>
       </c>
       <c r="K16" t="n">
         <v>18082600</v>
@@ -1281,7 +1281,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>990900</v>
+        <v>4698520</v>
       </c>
       <c r="K18" t="n">
         <v>19777800</v>
@@ -1375,7 +1375,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>881100</v>
+        <v>3079840</v>
       </c>
       <c r="K20" t="n">
         <v>14074400</v>
@@ -1469,7 +1469,7 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K22" t="n">
         <v>24</v>
@@ -1481,10 +1481,10 @@
         <v>0.6</v>
       </c>
       <c r="N22" t="n">
-        <v>344.714</v>
+        <v>340.404</v>
       </c>
       <c r="O22" t="n">
-        <v>347.16</v>
+        <v>342.85</v>
       </c>
     </row>
     <row r="23">
@@ -1528,10 +1528,10 @@
         <v>0.6</v>
       </c>
       <c r="N23" t="n">
-        <v>344.714</v>
+        <v>340.404</v>
       </c>
       <c r="O23" t="n">
-        <v>352.74</v>
+        <v>346.9</v>
       </c>
     </row>
     <row r="24">
@@ -1539,37 +1539,37 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6311290000000001</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>3.08061</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0.204872</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>1.94426</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>900526000</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2774170000</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>2575810000</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>11090200000</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>3600000000</v>
+        <v>3100000000</v>
       </c>
       <c r="M24" t="n">
         <v>0.6</v>
@@ -1578,7 +1578,7 @@
         <v>344.108</v>
       </c>
       <c r="O24" t="n">
-        <v>352.74</v>
+        <v>346.63</v>
       </c>
     </row>
     <row r="25">
@@ -1586,34 +1586,34 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C25" t="n">
-        <v>1.17348e-09</v>
+        <v>0.6311290000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>4.16667e-09</v>
+        <v>3.08061</v>
       </c>
       <c r="E25" t="n">
-        <v>0.281636</v>
+        <v>0.204872</v>
       </c>
       <c r="F25" t="n">
-        <v>4.889510000000001e-18</v>
+        <v>1.94426</v>
       </c>
       <c r="G25" t="n">
-        <v>720000000</v>
+        <v>900526000</v>
       </c>
       <c r="H25" t="n">
-        <v>3</v>
+        <v>2774170000</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>2575810000</v>
       </c>
       <c r="K25" t="n">
-        <v>15</v>
+        <v>11090200000</v>
       </c>
       <c r="L25" t="n">
         <v>3600000000</v>
@@ -1622,10 +1622,10 @@
         <v>0.6</v>
       </c>
       <c r="N25" t="n">
-        <v>350.151</v>
+        <v>344.108</v>
       </c>
       <c r="O25" t="n">
-        <v>350.2</v>
+        <v>352.74</v>
       </c>
     </row>
     <row r="26">
@@ -1633,35 +1633,35 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C26" t="n">
-        <v>8.44791e-09</v>
+        <v>1.17348e-09</v>
       </c>
       <c r="D26" t="n">
-        <v>2.77778e-08</v>
+        <v>4.16667e-09</v>
       </c>
       <c r="E26" t="n">
-        <v>0.304125</v>
+        <v>0.281636</v>
       </c>
       <c r="F26" t="n">
-        <v>2.34664e-16</v>
+        <v>4.889510000000001e-18</v>
       </c>
       <c r="G26" t="n">
-        <v>1044000000</v>
+        <v>720000000</v>
       </c>
       <c r="H26" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K26" t="n">
         <v>15</v>
       </c>
-      <c r="K26" t="n">
-        <v>100</v>
-      </c>
       <c r="L26" t="n">
         <v>3600000000</v>
       </c>
@@ -1669,10 +1669,10 @@
         <v>0.6</v>
       </c>
       <c r="N26" t="n">
-        <v>350.15</v>
+        <v>350.151</v>
       </c>
       <c r="O26" t="n">
-        <v>350.18</v>
+        <v>350.2</v>
       </c>
     </row>
     <row r="27">
@@ -1680,34 +1680,34 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C27" t="n">
-        <v>4.64603e-10</v>
+        <v>8.44791e-09</v>
       </c>
       <c r="D27" t="n">
-        <v>1.66667e-09</v>
+        <v>2.77778e-08</v>
       </c>
       <c r="E27" t="n">
-        <v>0.278762</v>
+        <v>0.304125</v>
       </c>
       <c r="F27" t="n">
-        <v>7.74338e-19</v>
+        <v>2.34664e-16</v>
       </c>
       <c r="G27" t="n">
-        <v>600000000</v>
+        <v>1044000000</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K27" t="n">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="L27" t="n">
         <v>3600000000</v>
@@ -1719,7 +1719,7 @@
         <v>350.15</v>
       </c>
       <c r="O27" t="n">
-        <v>350.17</v>
+        <v>350.18</v>
       </c>
     </row>
     <row r="28">
@@ -1727,7 +1727,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C28" t="n">
         <v>4.64603e-10</v>
@@ -1774,34 +1774,34 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C29" t="n">
-        <v>6.10341e-10</v>
+        <v>4.64603e-10</v>
       </c>
       <c r="D29" t="n">
-        <v>1.94444e-09</v>
+        <v>1.66667e-09</v>
       </c>
       <c r="E29" t="n">
-        <v>0.31389</v>
+        <v>0.278762</v>
       </c>
       <c r="F29" t="n">
-        <v>1.18677e-18</v>
+        <v>7.74338e-19</v>
       </c>
       <c r="G29" t="n">
-        <v>1028570000</v>
+        <v>600000000</v>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L29" t="n">
         <v>3600000000</v>
@@ -1810,10 +1810,10 @@
         <v>0.6</v>
       </c>
       <c r="N29" t="n">
-        <v>350.151</v>
+        <v>350.15</v>
       </c>
       <c r="O29" t="n">
-        <v>350.18</v>
+        <v>350.17</v>
       </c>
     </row>
     <row r="30">
@@ -1821,7 +1821,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C30" t="n">
         <v>6.10341e-10</v>
@@ -1868,34 +1868,34 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C31" t="n">
-        <v>1.45203e-09</v>
+        <v>6.10341e-10</v>
       </c>
       <c r="D31" t="n">
-        <v>4.72222e-09</v>
+        <v>1.94444e-09</v>
       </c>
       <c r="E31" t="n">
-        <v>0.30749</v>
+        <v>0.31389</v>
       </c>
       <c r="F31" t="n">
-        <v>6.85683e-18</v>
+        <v>1.18677e-18</v>
       </c>
       <c r="G31" t="n">
-        <v>847059000</v>
+        <v>1028570000</v>
       </c>
       <c r="H31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="L31" t="n">
         <v>3600000000</v>
@@ -1915,34 +1915,34 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C32" t="n">
-        <v>1.19266e-10</v>
+        <v>1.45203e-09</v>
       </c>
       <c r="D32" t="n">
-        <v>2.77778e-10</v>
+        <v>4.72222e-09</v>
       </c>
       <c r="E32" t="n">
-        <v>0.429359</v>
+        <v>0.30749</v>
       </c>
       <c r="F32" t="n">
-        <v>3.31295e-20</v>
+        <v>6.85683e-18</v>
       </c>
       <c r="G32" t="n">
-        <v>3600000000</v>
+        <v>847059000</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K32" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="L32" t="n">
         <v>3600000000</v>
@@ -1954,6 +1954,53 @@
         <v>350.151</v>
       </c>
       <c r="O32" t="n">
+        <v>350.18</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="n">
+        <v>31</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1.19266e-10</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2.77778e-10</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.429359</v>
+      </c>
+      <c r="F33" t="n">
+        <v>3.31295e-20</v>
+      </c>
+      <c r="G33" t="n">
+        <v>3600000000</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" t="n">
+        <v>3600000000</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N33" t="n">
+        <v>350.151</v>
+      </c>
+      <c r="O33" t="n">
         <v>350.23</v>
       </c>
     </row>
